--- a/Proyecto/Presentación/quarto presentación_files/gadm41_GTM_shp/indicadores_acceso_tecnologico.xlsx
+++ b/Proyecto/Presentación/quarto presentación_files/gadm41_GTM_shp/indicadores_acceso_tecnologico.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/D11B7E7C31B62C39/Escritorio/PROGRAMACIÓN II/programa-II/Proyecto/output/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d11b7e7c31b62c39/Escritorio/PROGRAMACIÓN II/programa-II/Proyecto/Presentación/quarto presentación_files/gadm41_GTM_shp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_3E5C4BAEF1248DD158C55A7E6BBD231897459A04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9610A05-B883-4287-BFC7-7C130EBAF257}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_3E5C4BAEF1248DD158C55A7E6BBD231897459A04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B5CF34C-1EC4-4BF8-B32A-AA70002FE41F}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="indicadores_basicos" sheetId="1" r:id="rId1"/>
@@ -133,11 +133,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,770 +485,770 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>56.4</v>
-      </c>
-      <c r="C2">
-        <v>30.73</v>
-      </c>
-      <c r="D2">
-        <v>69.2</v>
-      </c>
-      <c r="E2">
-        <v>10.24</v>
-      </c>
-      <c r="F2">
-        <v>36.880000000000003</v>
-      </c>
-      <c r="G2">
-        <v>36.67</v>
-      </c>
-      <c r="H2">
-        <v>167.7</v>
-      </c>
-      <c r="I2">
-        <v>404.86</v>
-      </c>
-      <c r="J2">
-        <v>14654.86531187161</v>
-      </c>
-      <c r="K2">
-        <v>77.576314310000001</v>
+      <c r="B2" s="2">
+        <v>67.405063291139228</v>
+      </c>
+      <c r="C2" s="2">
+        <v>38.522270221957399</v>
+      </c>
+      <c r="D2" s="2">
+        <v>72.978116079923879</v>
+      </c>
+      <c r="E2" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2" s="2">
+        <v>53.761236398044467</v>
+      </c>
+      <c r="G2" s="2">
+        <v>84.19052444894858</v>
+      </c>
+      <c r="H2" s="2">
+        <v>80.304878048780481</v>
+      </c>
+      <c r="I2" s="2">
+        <v>99.989911727616658</v>
+      </c>
+      <c r="J2" s="2">
+        <v>99.999742788163687</v>
+      </c>
+      <c r="K2" s="2">
+        <v>74.8</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>44.76</v>
-      </c>
-      <c r="C3">
-        <v>23.04</v>
-      </c>
-      <c r="D3">
-        <v>58.52</v>
-      </c>
-      <c r="E3">
-        <v>44.4</v>
-      </c>
-      <c r="F3">
-        <v>15.49</v>
-      </c>
-      <c r="G3">
-        <v>13.53</v>
-      </c>
-      <c r="H3">
-        <v>168.09</v>
-      </c>
-      <c r="I3">
-        <v>47.97</v>
-      </c>
-      <c r="J3">
-        <v>5502.5833595994081</v>
-      </c>
-      <c r="K3">
-        <v>43.468735770000002</v>
+      <c r="B3" s="2">
+        <v>48.987341772151893</v>
+      </c>
+      <c r="C3" s="2">
+        <v>27.066885148219871</v>
+      </c>
+      <c r="D3" s="2">
+        <v>52.654614652711707</v>
+      </c>
+      <c r="E3" s="2">
+        <v>59.902050811141727</v>
+      </c>
+      <c r="F3" s="2">
+        <v>20.028386689796559</v>
+      </c>
+      <c r="G3" s="2">
+        <v>25.563719280466181</v>
+      </c>
+      <c r="H3" s="2">
+        <v>80.542682926829272</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9.9798234552332907</v>
+      </c>
+      <c r="J3" s="2">
+        <v>32.135739837948599</v>
+      </c>
+      <c r="K3" s="2">
+        <v>41.31</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>47.32</v>
-      </c>
-      <c r="C4">
-        <v>22.53</v>
-      </c>
-      <c r="D4">
-        <v>66.05</v>
-      </c>
-      <c r="E4">
-        <v>12.8</v>
-      </c>
-      <c r="F4">
-        <v>15.62</v>
-      </c>
-      <c r="G4">
-        <v>29.89</v>
-      </c>
-      <c r="H4">
-        <v>133.18</v>
-      </c>
-      <c r="I4">
-        <v>54.61</v>
-      </c>
-      <c r="J4">
-        <v>6413.809557371761</v>
-      </c>
-      <c r="K4">
-        <v>56.074692450000001</v>
+      <c r="B4" s="2">
+        <v>53.037974683544299</v>
+      </c>
+      <c r="C4" s="2">
+        <v>26.30716520184717</v>
+      </c>
+      <c r="D4" s="2">
+        <v>66.983824928639379</v>
+      </c>
+      <c r="E4" s="2">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2">
+        <v>20.233401671660619</v>
+      </c>
+      <c r="G4" s="2">
+        <v>67.012921205979225</v>
+      </c>
+      <c r="H4" s="2">
+        <v>59.256097560975618</v>
+      </c>
+      <c r="I4" s="2">
+        <v>11.65447667087011</v>
+      </c>
+      <c r="J4" s="2">
+        <v>38.892465395183393</v>
+      </c>
+      <c r="K4" s="2">
+        <v>51.01</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="C5">
-        <v>18.809999999999999</v>
-      </c>
-      <c r="D5">
-        <v>55.73</v>
-      </c>
-      <c r="E5">
-        <v>50.26</v>
-      </c>
-      <c r="F5">
-        <v>17.28</v>
-      </c>
-      <c r="G5">
-        <v>14.9</v>
-      </c>
-      <c r="H5">
-        <v>75.27</v>
-      </c>
-      <c r="I5">
-        <v>18.809999999999999</v>
-      </c>
-      <c r="J5">
-        <v>2841.710966594324</v>
-      </c>
-      <c r="K5">
-        <v>36.326530650000002</v>
+      <c r="B5" s="2">
+        <v>36.392405063291143</v>
+      </c>
+      <c r="C5" s="2">
+        <v>20.765678534187391</v>
+      </c>
+      <c r="D5" s="2">
+        <v>47.345385347288293</v>
+      </c>
+      <c r="E5" s="2">
+        <v>50.933578206305476</v>
+      </c>
+      <c r="F5" s="2">
+        <v>22.851285286232461</v>
+      </c>
+      <c r="G5" s="2">
+        <v>29.03470990625792</v>
+      </c>
+      <c r="H5" s="2">
+        <v>23.945121951219509</v>
+      </c>
+      <c r="I5" s="2">
+        <v>2.6254728877679701</v>
+      </c>
+      <c r="J5" s="2">
+        <v>12.405419807301859</v>
+      </c>
+      <c r="K5" s="2">
+        <v>29.57</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>47.95</v>
-      </c>
-      <c r="C6">
-        <v>25.4</v>
-      </c>
-      <c r="D6">
-        <v>59.28</v>
-      </c>
-      <c r="E6">
-        <v>42.99</v>
-      </c>
-      <c r="F6">
-        <v>16.350000000000001</v>
-      </c>
-      <c r="G6">
-        <v>11.85</v>
-      </c>
-      <c r="H6">
-        <v>131</v>
-      </c>
-      <c r="I6">
-        <v>30.04</v>
-      </c>
-      <c r="J6">
-        <v>10861.05517605828</v>
-      </c>
-      <c r="K6">
-        <v>48.678756980000003</v>
+      <c r="B6" s="2">
+        <v>54.034810126582293</v>
+      </c>
+      <c r="C6" s="2">
+        <v>30.582451958885741</v>
+      </c>
+      <c r="D6" s="2">
+        <v>54.100856327307334</v>
+      </c>
+      <c r="E6" s="2">
+        <v>62.059993878175703</v>
+      </c>
+      <c r="F6" s="2">
+        <v>21.38463964674342</v>
+      </c>
+      <c r="G6" s="2">
+        <v>21.30732201672156</v>
+      </c>
+      <c r="H6" s="2">
+        <v>57.926829268292678</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5.4577553593947039</v>
+      </c>
+      <c r="J6" s="2">
+        <v>71.86871015695499</v>
+      </c>
+      <c r="K6" s="2">
+        <v>44.23</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>44.69</v>
-      </c>
-      <c r="C7">
-        <v>21.98</v>
-      </c>
-      <c r="D7">
-        <v>58.33</v>
-      </c>
-      <c r="E7">
-        <v>54.36</v>
-      </c>
-      <c r="F7">
-        <v>17.95</v>
-      </c>
-      <c r="G7">
-        <v>6.91</v>
-      </c>
-      <c r="H7">
-        <v>133.5</v>
-      </c>
-      <c r="I7">
-        <v>21.57</v>
-      </c>
-      <c r="J7">
-        <v>4447.2811944283394</v>
-      </c>
-      <c r="K7">
-        <v>38.768372200000002</v>
+      <c r="B7" s="2">
+        <v>48.87658227848101</v>
+      </c>
+      <c r="C7" s="2">
+        <v>25.487859377327581</v>
+      </c>
+      <c r="D7" s="2">
+        <v>52.293054234062787</v>
+      </c>
+      <c r="E7" s="2">
+        <v>44.658708295071939</v>
+      </c>
+      <c r="F7" s="2">
+        <v>23.90790096199337</v>
+      </c>
+      <c r="G7" s="2">
+        <v>8.7914872054725119</v>
+      </c>
+      <c r="H7" s="2">
+        <v>59.451219512195117</v>
+      </c>
+      <c r="I7" s="2">
+        <v>3.3215636822194199</v>
+      </c>
+      <c r="J7" s="2">
+        <v>24.310693622806848</v>
+      </c>
+      <c r="K7" s="2">
+        <v>34.94</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>35.840000000000003</v>
-      </c>
-      <c r="C8">
-        <v>17.82</v>
-      </c>
-      <c r="D8">
-        <v>53.3</v>
-      </c>
-      <c r="E8">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="F8">
-        <v>21.05</v>
-      </c>
-      <c r="G8">
-        <v>17.03</v>
-      </c>
-      <c r="H8">
-        <v>78.09</v>
-      </c>
-      <c r="I8">
-        <v>20.309999999999999</v>
-      </c>
-      <c r="J8">
-        <v>3253.97911654683</v>
-      </c>
-      <c r="K8">
-        <v>41.421687470000002</v>
+      <c r="B8" s="2">
+        <v>34.87341772151899</v>
+      </c>
+      <c r="C8" s="2">
+        <v>19.290928050052141</v>
+      </c>
+      <c r="D8" s="2">
+        <v>42.721217887725963</v>
+      </c>
+      <c r="E8" s="2">
+        <v>73.82920110192839</v>
+      </c>
+      <c r="F8" s="2">
+        <v>28.79671976029017</v>
+      </c>
+      <c r="G8" s="2">
+        <v>34.431213579934131</v>
+      </c>
+      <c r="H8" s="2">
+        <v>25.664634146341459</v>
+      </c>
+      <c r="I8" s="2">
+        <v>3.0037831021437569</v>
+      </c>
+      <c r="J8" s="2">
+        <v>15.46238058392113</v>
+      </c>
+      <c r="K8" s="2">
+        <v>33.36</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>32.520000000000003</v>
-      </c>
-      <c r="C9">
-        <v>16.309999999999999</v>
-      </c>
-      <c r="D9">
-        <v>48.51</v>
-      </c>
-      <c r="E9">
-        <v>50.41</v>
-      </c>
-      <c r="F9">
-        <v>17.02</v>
-      </c>
-      <c r="G9">
-        <v>13.58</v>
-      </c>
-      <c r="H9">
-        <v>67.34</v>
-      </c>
-      <c r="I9">
-        <v>24.89</v>
-      </c>
-      <c r="J9">
-        <v>3705.3634024380449</v>
-      </c>
-      <c r="K9">
-        <v>32.234150679999999</v>
+      <c r="B9" s="2">
+        <v>29.62025316455696</v>
+      </c>
+      <c r="C9" s="2">
+        <v>17.04156115000745</v>
+      </c>
+      <c r="D9" s="2">
+        <v>33.606089438629873</v>
+      </c>
+      <c r="E9" s="2">
+        <v>50.704009794918903</v>
+      </c>
+      <c r="F9" s="2">
+        <v>22.44125532250434</v>
+      </c>
+      <c r="G9" s="2">
+        <v>25.690397770458581</v>
+      </c>
+      <c r="H9" s="2">
+        <v>19.109756097560979</v>
+      </c>
+      <c r="I9" s="2">
+        <v>4.1588902900378324</v>
+      </c>
+      <c r="J9" s="2">
+        <v>18.809386791678651</v>
+      </c>
+      <c r="K9" s="2">
+        <v>26.42</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>44.65</v>
-      </c>
-      <c r="C10">
-        <v>23.89</v>
-      </c>
-      <c r="D10">
-        <v>58.31</v>
-      </c>
-      <c r="E10">
-        <v>43.76</v>
-      </c>
-      <c r="F10">
-        <v>25.74</v>
-      </c>
-      <c r="G10">
-        <v>19.77</v>
-      </c>
-      <c r="H10">
-        <v>116.41</v>
-      </c>
-      <c r="I10">
-        <v>154.41999999999999</v>
-      </c>
-      <c r="J10">
-        <v>7089.6459617951687</v>
-      </c>
-      <c r="K10">
-        <v>50.2077958</v>
+      <c r="B10" s="2">
+        <v>48.813291139240498</v>
+      </c>
+      <c r="C10" s="2">
+        <v>28.333085058841061</v>
+      </c>
+      <c r="D10" s="2">
+        <v>52.254995242626073</v>
+      </c>
+      <c r="E10" s="2">
+        <v>60.88154269972452</v>
+      </c>
+      <c r="F10" s="2">
+        <v>36.193029490616617</v>
+      </c>
+      <c r="G10" s="2">
+        <v>41.373194831517608</v>
+      </c>
+      <c r="H10" s="2">
+        <v>49.030487804878049</v>
+      </c>
+      <c r="I10" s="2">
+        <v>36.827238335435062</v>
+      </c>
+      <c r="J10" s="2">
+        <v>43.903779948519038</v>
+      </c>
+      <c r="K10" s="2">
+        <v>44.85</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>39.049999999999997</v>
-      </c>
-      <c r="C11">
-        <v>19.04</v>
-      </c>
-      <c r="D11">
-        <v>52.36</v>
-      </c>
-      <c r="E11">
-        <v>50.69</v>
-      </c>
-      <c r="F11">
-        <v>12.35</v>
-      </c>
-      <c r="G11">
-        <v>10.19</v>
-      </c>
-      <c r="H11">
-        <v>103.76</v>
-      </c>
-      <c r="I11">
-        <v>23.16</v>
-      </c>
-      <c r="J11">
-        <v>4277.2875928465764</v>
-      </c>
-      <c r="K11">
-        <v>36.171659529999999</v>
+      <c r="B11" s="2">
+        <v>39.952531645569607</v>
+      </c>
+      <c r="C11" s="2">
+        <v>21.108297333531951</v>
+      </c>
+      <c r="D11" s="2">
+        <v>40.932445290199801</v>
+      </c>
+      <c r="E11" s="2">
+        <v>50.275482093663918</v>
+      </c>
+      <c r="F11" s="2">
+        <v>15.07648635861851</v>
+      </c>
+      <c r="G11" s="2">
+        <v>17.101596148973901</v>
+      </c>
+      <c r="H11" s="2">
+        <v>41.31707317073171</v>
+      </c>
+      <c r="I11" s="2">
+        <v>3.722572509457756</v>
+      </c>
+      <c r="J11" s="2">
+        <v>23.05019418240245</v>
+      </c>
+      <c r="K11" s="2">
+        <v>30.02</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>38.979999999999997</v>
-      </c>
-      <c r="C12">
-        <v>19.53</v>
-      </c>
-      <c r="D12">
-        <v>55.3</v>
-      </c>
-      <c r="E12">
-        <v>47.41</v>
-      </c>
-      <c r="F12">
-        <v>13.36</v>
-      </c>
-      <c r="G12">
-        <v>10.97</v>
-      </c>
-      <c r="H12">
-        <v>117.38</v>
-      </c>
-      <c r="I12">
-        <v>27.74</v>
-      </c>
-      <c r="J12">
-        <v>5334.3289282319183</v>
-      </c>
-      <c r="K12">
-        <v>38.647416249999999</v>
+      <c r="B12" s="2">
+        <v>39.841772151898716</v>
+      </c>
+      <c r="C12" s="2">
+        <v>21.838224340831221</v>
+      </c>
+      <c r="D12" s="2">
+        <v>46.52711703139866</v>
+      </c>
+      <c r="E12" s="2">
+        <v>55.295378022650773</v>
+      </c>
+      <c r="F12" s="2">
+        <v>16.669295063870049</v>
+      </c>
+      <c r="G12" s="2">
+        <v>19.077780592855341</v>
+      </c>
+      <c r="H12" s="2">
+        <v>49.621951219512198</v>
+      </c>
+      <c r="I12" s="2">
+        <v>4.8776796973518266</v>
+      </c>
+      <c r="J12" s="2">
+        <v>30.888136312810779</v>
+      </c>
+      <c r="K12" s="2">
+        <v>33.35</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>36.119999999999997</v>
-      </c>
-      <c r="C13">
-        <v>19.690000000000001</v>
-      </c>
-      <c r="D13">
-        <v>50.81</v>
-      </c>
-      <c r="E13">
-        <v>75.36</v>
-      </c>
-      <c r="F13">
-        <v>11.71</v>
-      </c>
-      <c r="G13">
-        <v>10.95</v>
-      </c>
-      <c r="H13">
-        <v>80.709999999999994</v>
-      </c>
-      <c r="I13">
-        <v>17.04</v>
-      </c>
-      <c r="J13">
-        <v>4681.3897633864817</v>
-      </c>
-      <c r="K13">
-        <v>29.827691529999999</v>
+      <c r="B13" s="2">
+        <v>35.316455696202517</v>
+      </c>
+      <c r="C13" s="2">
+        <v>22.076567853418741</v>
+      </c>
+      <c r="D13" s="2">
+        <v>37.982873453853472</v>
+      </c>
+      <c r="E13" s="2">
+        <v>12.519130700948891</v>
+      </c>
+      <c r="F13" s="2">
+        <v>14.06718183251853</v>
+      </c>
+      <c r="G13" s="2">
+        <v>19.02710919685838</v>
+      </c>
+      <c r="H13" s="2">
+        <v>27.262195121951219</v>
+      </c>
+      <c r="I13" s="2">
+        <v>2.179066834804539</v>
+      </c>
+      <c r="J13" s="2">
+        <v>26.046604371328058</v>
+      </c>
+      <c r="K13" s="2">
+        <v>23.32</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>32.69</v>
-      </c>
-      <c r="C14">
-        <v>17.39</v>
-      </c>
-      <c r="D14">
-        <v>49.35</v>
-      </c>
-      <c r="E14">
-        <v>64.52</v>
-      </c>
-      <c r="F14">
-        <v>15.5</v>
-      </c>
-      <c r="G14">
-        <v>12.22</v>
-      </c>
-      <c r="H14">
-        <v>81.84</v>
-      </c>
-      <c r="I14">
-        <v>16.09</v>
-      </c>
-      <c r="J14">
-        <v>2860.3775419277249</v>
-      </c>
-      <c r="K14">
-        <v>30.658266730000001</v>
+      <c r="B14" s="2">
+        <v>29.889240506329109</v>
+      </c>
+      <c r="C14" s="2">
+        <v>18.650379859973189</v>
+      </c>
+      <c r="D14" s="2">
+        <v>35.204567078972403</v>
+      </c>
+      <c r="E14" s="2">
+        <v>29.10927456382003</v>
+      </c>
+      <c r="F14" s="2">
+        <v>20.044157073016869</v>
+      </c>
+      <c r="G14" s="2">
+        <v>22.244742842665321</v>
+      </c>
+      <c r="H14" s="2">
+        <v>27.95121951219512</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1.939470365699874</v>
+      </c>
+      <c r="J14" s="2">
+        <v>12.54383212131299</v>
+      </c>
+      <c r="K14" s="2">
+        <v>23.64</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>27.64</v>
-      </c>
-      <c r="C15">
-        <v>14.43</v>
-      </c>
-      <c r="D15">
-        <v>46.65</v>
-      </c>
-      <c r="E15">
-        <v>63.33</v>
-      </c>
-      <c r="F15">
-        <v>8.48</v>
-      </c>
-      <c r="G15">
-        <v>8.49</v>
-      </c>
-      <c r="H15">
-        <v>67.709999999999994</v>
-      </c>
-      <c r="I15">
-        <v>8.3699999999999992</v>
-      </c>
-      <c r="J15">
-        <v>2601.343610276273</v>
-      </c>
-      <c r="K15">
-        <v>23.099284000000001</v>
+      <c r="B15" s="2">
+        <v>21.898734177215189</v>
+      </c>
+      <c r="C15" s="2">
+        <v>14.24102487710412</v>
+      </c>
+      <c r="D15" s="2">
+        <v>30.06660323501427</v>
+      </c>
+      <c r="E15" s="2">
+        <v>30.93051729415367</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8.9733480523576734</v>
+      </c>
+      <c r="G15" s="2">
+        <v>12.79452748923233</v>
+      </c>
+      <c r="H15" s="2">
+        <v>19.33536585365853</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>10.62310026520626</v>
+      </c>
+      <c r="K15" s="2">
+        <v>17.71</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>29.8</v>
-      </c>
-      <c r="C16">
-        <v>16.079999999999998</v>
-      </c>
-      <c r="D16">
-        <v>50.71</v>
-      </c>
-      <c r="E16">
-        <v>65.260000000000005</v>
-      </c>
-      <c r="F16">
-        <v>10.07</v>
-      </c>
-      <c r="G16">
-        <v>14.64</v>
-      </c>
-      <c r="H16">
-        <v>88.49</v>
-      </c>
-      <c r="I16">
-        <v>14.32</v>
-      </c>
-      <c r="J16">
-        <v>2997.2282568044861</v>
-      </c>
-      <c r="K16">
-        <v>29.059082320000002</v>
+      <c r="B16" s="2">
+        <v>25.316455696202532</v>
+      </c>
+      <c r="C16" s="2">
+        <v>16.69894235066289</v>
+      </c>
+      <c r="D16" s="2">
+        <v>37.792578496669833</v>
+      </c>
+      <c r="E16" s="2">
+        <v>27.976737067646159</v>
+      </c>
+      <c r="F16" s="2">
+        <v>11.48083898438732</v>
+      </c>
+      <c r="G16" s="2">
+        <v>28.375981758297449</v>
+      </c>
+      <c r="H16" s="2">
+        <v>32.006097560975597</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1.493064312736444</v>
+      </c>
+      <c r="J16" s="2">
+        <v>13.55857766418057</v>
+      </c>
+      <c r="K16" s="2">
+        <v>22.55</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>21.62</v>
-      </c>
-      <c r="C17">
-        <v>9.25</v>
-      </c>
-      <c r="D17">
-        <v>37.58</v>
-      </c>
-      <c r="E17">
-        <v>69.790000000000006</v>
-      </c>
-      <c r="F17">
-        <v>6.14</v>
-      </c>
-      <c r="G17">
-        <v>7.36</v>
-      </c>
-      <c r="H17">
-        <v>51.95</v>
-      </c>
-      <c r="I17">
-        <v>8.94</v>
-      </c>
-      <c r="J17">
-        <v>3424.9822825369802</v>
-      </c>
-      <c r="K17">
-        <v>14.070769609999999</v>
+      <c r="B17" s="2">
+        <v>12.37341772151899</v>
+      </c>
+      <c r="C17" s="2">
+        <v>6.5246536570832721</v>
+      </c>
+      <c r="D17" s="2">
+        <v>12.806850618458601</v>
+      </c>
+      <c r="E17" s="2">
+        <v>21.043771043771041</v>
+      </c>
+      <c r="F17" s="2">
+        <v>5.2830783788046043</v>
+      </c>
+      <c r="G17" s="2">
+        <v>9.9315936154041058</v>
+      </c>
+      <c r="H17" s="2">
+        <v>9.7256097560975618</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.13619167717528349</v>
+      </c>
+      <c r="J17" s="2">
+        <v>16.73036592591232</v>
+      </c>
+      <c r="K17" s="2">
+        <v>11.12</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>42.63</v>
-      </c>
-      <c r="C18">
-        <v>22.49</v>
-      </c>
-      <c r="D18">
-        <v>52.29</v>
-      </c>
-      <c r="E18">
-        <v>63.06</v>
-      </c>
-      <c r="F18">
-        <v>16.350000000000001</v>
-      </c>
-      <c r="G18">
-        <v>13.88</v>
-      </c>
-      <c r="H18">
-        <v>127.78</v>
-      </c>
-      <c r="I18">
-        <v>18.95</v>
-      </c>
-      <c r="J18">
-        <v>5385.8394952948338</v>
-      </c>
-      <c r="K18">
-        <v>37.506132200000003</v>
+      <c r="B18" s="2">
+        <v>45.617088607594937</v>
+      </c>
+      <c r="C18" s="2">
+        <v>26.247579323700279</v>
+      </c>
+      <c r="D18" s="2">
+        <v>40.799238820171247</v>
+      </c>
+      <c r="E18" s="2">
+        <v>31.343740434649529</v>
+      </c>
+      <c r="F18" s="2">
+        <v>21.38463964674342</v>
+      </c>
+      <c r="G18" s="2">
+        <v>26.450468710412981</v>
+      </c>
+      <c r="H18" s="2">
+        <v>55.963414634146353</v>
+      </c>
+      <c r="I18" s="2">
+        <v>2.6607818411097099</v>
+      </c>
+      <c r="J18" s="2">
+        <v>31.270086223593101</v>
+      </c>
+      <c r="K18" s="2">
+        <v>33.39</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
-        <v>41.53</v>
-      </c>
-      <c r="C19">
-        <v>21.34</v>
-      </c>
-      <c r="D19">
-        <v>51.11</v>
-      </c>
-      <c r="E19">
-        <v>63.21</v>
-      </c>
-      <c r="F19">
-        <v>24.37</v>
-      </c>
-      <c r="G19">
-        <v>11.15</v>
-      </c>
-      <c r="H19">
-        <v>134.68</v>
-      </c>
-      <c r="I19">
-        <v>45.02</v>
-      </c>
-      <c r="J19">
-        <v>6539.4225553021897</v>
-      </c>
-      <c r="K19">
-        <v>39.219556609999998</v>
+      <c r="B19" s="2">
+        <v>43.87658227848101</v>
+      </c>
+      <c r="C19" s="2">
+        <v>24.53448532697751</v>
+      </c>
+      <c r="D19" s="2">
+        <v>38.553758325404367</v>
+      </c>
+      <c r="E19" s="2">
+        <v>31.114172023262942</v>
+      </c>
+      <c r="F19" s="2">
+        <v>34.032486989433849</v>
+      </c>
+      <c r="G19" s="2">
+        <v>19.533823156827971</v>
+      </c>
+      <c r="H19" s="2">
+        <v>60.170731707317081</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9.2358133669609082</v>
+      </c>
+      <c r="J19" s="2">
+        <v>39.823883472837743</v>
+      </c>
+      <c r="K19" s="2">
+        <v>35.46</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20">
-        <v>41.67</v>
-      </c>
-      <c r="C20">
-        <v>21.28</v>
-      </c>
-      <c r="D20">
-        <v>55.41</v>
-      </c>
-      <c r="E20">
-        <v>57.12</v>
-      </c>
-      <c r="F20">
-        <v>19.760000000000002</v>
-      </c>
-      <c r="G20">
-        <v>14.71</v>
-      </c>
-      <c r="H20">
-        <v>127.58</v>
-      </c>
-      <c r="I20">
-        <v>49.99</v>
-      </c>
-      <c r="J20">
-        <v>7132.5969764371694</v>
-      </c>
-      <c r="K20">
-        <v>41.535291579999999</v>
+      <c r="B20" s="2">
+        <v>44.098101265822777</v>
+      </c>
+      <c r="C20" s="2">
+        <v>24.445106509757188</v>
+      </c>
+      <c r="D20" s="2">
+        <v>46.736441484300649</v>
+      </c>
+      <c r="E20" s="2">
+        <v>40.434649525558633</v>
+      </c>
+      <c r="F20" s="2">
+        <v>26.7623403248699</v>
+      </c>
+      <c r="G20" s="2">
+        <v>28.553331644286811</v>
+      </c>
+      <c r="H20" s="2">
+        <v>55.841463414634141</v>
+      </c>
+      <c r="I20" s="2">
+        <v>10.48928121059269</v>
+      </c>
+      <c r="J20" s="2">
+        <v>44.222260934963707</v>
+      </c>
+      <c r="K20" s="2">
+        <v>37.31</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>34.24</v>
-      </c>
-      <c r="C21">
-        <v>17.23</v>
-      </c>
-      <c r="D21">
-        <v>50.4</v>
-      </c>
-      <c r="E21">
-        <v>64.180000000000007</v>
-      </c>
-      <c r="F21">
-        <v>24.74</v>
-      </c>
-      <c r="G21">
-        <v>11.23</v>
-      </c>
-      <c r="H21">
-        <v>106.25</v>
-      </c>
-      <c r="I21">
-        <v>27.66</v>
-      </c>
-      <c r="J21">
-        <v>4013.8238973598141</v>
-      </c>
-      <c r="K21">
-        <v>34.229939829999999</v>
+      <c r="B21" s="2">
+        <v>32.341772151898738</v>
+      </c>
+      <c r="C21" s="2">
+        <v>18.412036347385669</v>
+      </c>
+      <c r="D21" s="2">
+        <v>37.202664129400567</v>
+      </c>
+      <c r="E21" s="2">
+        <v>29.62962962962963</v>
+      </c>
+      <c r="F21" s="2">
+        <v>34.615991168585388</v>
+      </c>
+      <c r="G21" s="2">
+        <v>19.736508740815811</v>
+      </c>
+      <c r="H21" s="2">
+        <v>42.835365853658537</v>
+      </c>
+      <c r="I21" s="2">
+        <v>4.8575031525851191</v>
+      </c>
+      <c r="J21" s="2">
+        <v>21.096615708637302</v>
+      </c>
+      <c r="K21" s="2">
+        <v>28.74</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>32.76</v>
-      </c>
-      <c r="C22">
-        <v>19.16</v>
-      </c>
-      <c r="D22">
-        <v>49.28</v>
-      </c>
-      <c r="E22">
-        <v>42.43</v>
-      </c>
-      <c r="F22">
-        <v>20.309999999999999</v>
-      </c>
-      <c r="G22">
-        <v>12.89</v>
-      </c>
-      <c r="H22">
-        <v>94.22</v>
-      </c>
-      <c r="I22">
-        <v>21.79</v>
-      </c>
-      <c r="J22">
-        <v>3297.504029218479</v>
-      </c>
-      <c r="K22">
-        <v>37.707302460000001</v>
+      <c r="B22" s="2">
+        <v>29.999999999999989</v>
+      </c>
+      <c r="C22" s="2">
+        <v>21.28705496797259</v>
+      </c>
+      <c r="D22" s="2">
+        <v>35.071360608943863</v>
+      </c>
+      <c r="E22" s="2">
+        <v>62.917049280685653</v>
+      </c>
+      <c r="F22" s="2">
+        <v>27.62971140198707</v>
+      </c>
+      <c r="G22" s="2">
+        <v>23.942234608563471</v>
+      </c>
+      <c r="H22" s="2">
+        <v>35.5</v>
+      </c>
+      <c r="I22" s="2">
+        <v>3.377049180327869</v>
+      </c>
+      <c r="J22" s="2">
+        <v>15.78511701373832</v>
+      </c>
+      <c r="K22" s="2">
+        <v>30.42</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23">
-        <v>44.26</v>
-      </c>
-      <c r="C23">
-        <v>23.97</v>
-      </c>
-      <c r="D23">
-        <v>60.09</v>
-      </c>
-      <c r="E23">
-        <v>52.28</v>
-      </c>
-      <c r="F23">
-        <v>21.69</v>
-      </c>
-      <c r="G23">
-        <v>9.56</v>
-      </c>
-      <c r="H23">
-        <v>126.78</v>
-      </c>
-      <c r="I23">
-        <v>93.56</v>
-      </c>
-      <c r="J23">
-        <v>3875.954919188006</v>
-      </c>
-      <c r="K23">
-        <v>41.69458479</v>
+      <c r="B23" s="2">
+        <v>48.196202531645568</v>
+      </c>
+      <c r="C23" s="2">
+        <v>28.45225681513481</v>
+      </c>
+      <c r="D23" s="2">
+        <v>55.642245480494758</v>
+      </c>
+      <c r="E23" s="2">
+        <v>47.842056932966031</v>
+      </c>
+      <c r="F23" s="2">
+        <v>29.806024286390159</v>
+      </c>
+      <c r="G23" s="2">
+        <v>15.50544717506968</v>
+      </c>
+      <c r="H23" s="2">
+        <v>55.353658536585371</v>
+      </c>
+      <c r="I23" s="2">
+        <v>21.477931904161409</v>
+      </c>
+      <c r="J23" s="2">
+        <v>20.074319762097769</v>
+      </c>
+      <c r="K23" s="2">
+        <v>37.46</v>
       </c>
     </row>
   </sheetData>

--- a/Proyecto/Presentación/quarto presentación_files/gadm41_GTM_shp/indicadores_acceso_tecnologico.xlsx
+++ b/Proyecto/Presentación/quarto presentación_files/gadm41_GTM_shp/indicadores_acceso_tecnologico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d11b7e7c31b62c39/Escritorio/PROGRAMACIÓN II/programa-II/Proyecto/Presentación/quarto presentación_files/gadm41_GTM_shp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_3E5C4BAEF1248DD158C55A7E6BBD231897459A04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B5CF34C-1EC4-4BF8-B32A-AA70002FE41F}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_3E5C4BAEF1248DD158C55A7E6BBD231897459A04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3FA8EBC-064D-4734-9D67-ED1E02927E40}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,20 @@
     <sheet name="indicadores_basicos" sheetId="1" r:id="rId1"/>
     <sheet name="diccionario_variables" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -154,6 +167,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -443,10 +460,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,775 +498,995 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>67.405063291139228</v>
+        <v>67.41</v>
       </c>
       <c r="C2" s="2">
-        <v>38.522270221957399</v>
+        <v>38.520000000000003</v>
       </c>
       <c r="D2" s="2">
-        <v>72.978116079923879</v>
+        <v>72.98</v>
       </c>
       <c r="E2" s="2">
         <v>100</v>
       </c>
       <c r="F2" s="2">
-        <v>53.761236398044467</v>
+        <v>53.76</v>
       </c>
       <c r="G2" s="2">
-        <v>84.19052444894858</v>
+        <v>84.19</v>
       </c>
       <c r="H2" s="2">
-        <v>80.304878048780481</v>
+        <v>80.3</v>
       </c>
       <c r="I2" s="2">
-        <v>99.989911727616658</v>
+        <v>99.99</v>
       </c>
       <c r="J2" s="2">
-        <v>99.999742788163687</v>
+        <v>100</v>
       </c>
       <c r="K2" s="2">
         <v>74.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>48.987341772151893</v>
+        <v>48.99</v>
       </c>
       <c r="C3" s="2">
-        <v>27.066885148219871</v>
+        <v>27.07</v>
       </c>
       <c r="D3" s="2">
-        <v>52.654614652711707</v>
+        <v>52.65</v>
       </c>
       <c r="E3" s="2">
-        <v>59.902050811141727</v>
+        <v>59.9</v>
       </c>
       <c r="F3" s="2">
-        <v>20.028386689796559</v>
+        <v>20.03</v>
       </c>
       <c r="G3" s="2">
-        <v>25.563719280466181</v>
+        <v>25.56</v>
       </c>
       <c r="H3" s="2">
-        <v>80.542682926829272</v>
+        <v>80.540000000000006</v>
       </c>
       <c r="I3" s="2">
-        <v>9.9798234552332907</v>
+        <v>9.98</v>
       </c>
       <c r="J3" s="2">
-        <v>32.135739837948599</v>
+        <v>32.14</v>
       </c>
       <c r="K3" s="2">
         <v>41.31</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>53.037974683544299</v>
+        <v>53.04</v>
       </c>
       <c r="C4" s="2">
-        <v>26.30716520184717</v>
+        <v>26.31</v>
       </c>
       <c r="D4" s="2">
-        <v>66.983824928639379</v>
+        <v>66.98</v>
       </c>
       <c r="E4" s="2">
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>20.233401671660619</v>
+        <v>20.23</v>
       </c>
       <c r="G4" s="2">
-        <v>67.012921205979225</v>
+        <v>67.010000000000005</v>
       </c>
       <c r="H4" s="2">
-        <v>59.256097560975618</v>
+        <v>59.26</v>
       </c>
       <c r="I4" s="2">
-        <v>11.65447667087011</v>
+        <v>11.65</v>
       </c>
       <c r="J4" s="2">
-        <v>38.892465395183393</v>
+        <v>38.89</v>
       </c>
       <c r="K4" s="2">
         <v>51.01</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>36.392405063291143</v>
+        <v>36.39</v>
       </c>
       <c r="C5" s="2">
-        <v>20.765678534187391</v>
+        <v>20.77</v>
       </c>
       <c r="D5" s="2">
-        <v>47.345385347288293</v>
+        <v>47.35</v>
       </c>
       <c r="E5" s="2">
-        <v>50.933578206305476</v>
+        <v>50.93</v>
       </c>
       <c r="F5" s="2">
-        <v>22.851285286232461</v>
+        <v>22.85</v>
       </c>
       <c r="G5" s="2">
-        <v>29.03470990625792</v>
+        <v>29.03</v>
       </c>
       <c r="H5" s="2">
-        <v>23.945121951219509</v>
+        <v>23.95</v>
       </c>
       <c r="I5" s="2">
-        <v>2.6254728877679701</v>
+        <v>2.63</v>
       </c>
       <c r="J5" s="2">
-        <v>12.405419807301859</v>
+        <v>12.41</v>
       </c>
       <c r="K5" s="2">
         <v>29.57</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>54.034810126582293</v>
+        <v>54.03</v>
       </c>
       <c r="C6" s="2">
-        <v>30.582451958885741</v>
+        <v>30.58</v>
       </c>
       <c r="D6" s="2">
-        <v>54.100856327307334</v>
+        <v>54.1</v>
       </c>
       <c r="E6" s="2">
-        <v>62.059993878175703</v>
+        <v>62.06</v>
       </c>
       <c r="F6" s="2">
-        <v>21.38463964674342</v>
+        <v>21.38</v>
       </c>
       <c r="G6" s="2">
-        <v>21.30732201672156</v>
+        <v>21.31</v>
       </c>
       <c r="H6" s="2">
-        <v>57.926829268292678</v>
+        <v>57.93</v>
       </c>
       <c r="I6" s="2">
-        <v>5.4577553593947039</v>
+        <v>5.46</v>
       </c>
       <c r="J6" s="2">
-        <v>71.86871015695499</v>
+        <v>71.87</v>
       </c>
       <c r="K6" s="2">
         <v>44.23</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>48.87658227848101</v>
+        <v>48.88</v>
       </c>
       <c r="C7" s="2">
-        <v>25.487859377327581</v>
+        <v>25.49</v>
       </c>
       <c r="D7" s="2">
-        <v>52.293054234062787</v>
+        <v>52.29</v>
       </c>
       <c r="E7" s="2">
-        <v>44.658708295071939</v>
+        <v>44.66</v>
       </c>
       <c r="F7" s="2">
-        <v>23.90790096199337</v>
+        <v>23.91</v>
       </c>
       <c r="G7" s="2">
-        <v>8.7914872054725119</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="H7" s="2">
-        <v>59.451219512195117</v>
+        <v>59.45</v>
       </c>
       <c r="I7" s="2">
-        <v>3.3215636822194199</v>
+        <v>3.32</v>
       </c>
       <c r="J7" s="2">
-        <v>24.310693622806848</v>
+        <v>24.31</v>
       </c>
       <c r="K7" s="2">
         <v>34.94</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>34.87341772151899</v>
+        <v>34.869999999999997</v>
       </c>
       <c r="C8" s="2">
-        <v>19.290928050052141</v>
+        <v>19.29</v>
       </c>
       <c r="D8" s="2">
-        <v>42.721217887725963</v>
+        <v>42.72</v>
       </c>
       <c r="E8" s="2">
-        <v>73.82920110192839</v>
+        <v>73.83</v>
       </c>
       <c r="F8" s="2">
-        <v>28.79671976029017</v>
+        <v>28.8</v>
       </c>
       <c r="G8" s="2">
-        <v>34.431213579934131</v>
+        <v>34.43</v>
       </c>
       <c r="H8" s="2">
-        <v>25.664634146341459</v>
+        <v>25.66</v>
       </c>
       <c r="I8" s="2">
-        <v>3.0037831021437569</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2">
-        <v>15.46238058392113</v>
+        <v>15.46</v>
       </c>
       <c r="K8" s="2">
         <v>33.36</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>29.62025316455696</v>
+        <v>29.62</v>
       </c>
       <c r="C9" s="2">
-        <v>17.04156115000745</v>
+        <v>17.04</v>
       </c>
       <c r="D9" s="2">
-        <v>33.606089438629873</v>
+        <v>33.61</v>
       </c>
       <c r="E9" s="2">
-        <v>50.704009794918903</v>
+        <v>50.7</v>
       </c>
       <c r="F9" s="2">
-        <v>22.44125532250434</v>
+        <v>22.44</v>
       </c>
       <c r="G9" s="2">
-        <v>25.690397770458581</v>
+        <v>25.69</v>
       </c>
       <c r="H9" s="2">
-        <v>19.109756097560979</v>
+        <v>19.11</v>
       </c>
       <c r="I9" s="2">
-        <v>4.1588902900378324</v>
+        <v>4.16</v>
       </c>
       <c r="J9" s="2">
-        <v>18.809386791678651</v>
+        <v>18.809999999999999</v>
       </c>
       <c r="K9" s="2">
         <v>26.42</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>48.813291139240498</v>
+        <v>48.81</v>
       </c>
       <c r="C10" s="2">
-        <v>28.333085058841061</v>
+        <v>28.33</v>
       </c>
       <c r="D10" s="2">
-        <v>52.254995242626073</v>
+        <v>52.25</v>
       </c>
       <c r="E10" s="2">
-        <v>60.88154269972452</v>
+        <v>60.88</v>
       </c>
       <c r="F10" s="2">
-        <v>36.193029490616617</v>
+        <v>36.19</v>
       </c>
       <c r="G10" s="2">
-        <v>41.373194831517608</v>
+        <v>41.37</v>
       </c>
       <c r="H10" s="2">
-        <v>49.030487804878049</v>
+        <v>49.03</v>
       </c>
       <c r="I10" s="2">
-        <v>36.827238335435062</v>
+        <v>36.83</v>
       </c>
       <c r="J10" s="2">
-        <v>43.903779948519038</v>
+        <v>43.9</v>
       </c>
       <c r="K10" s="2">
         <v>44.85</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>39.952531645569607</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="C11" s="2">
-        <v>21.108297333531951</v>
+        <v>21.11</v>
       </c>
       <c r="D11" s="2">
-        <v>40.932445290199801</v>
+        <v>40.93</v>
       </c>
       <c r="E11" s="2">
-        <v>50.275482093663918</v>
+        <v>50.28</v>
       </c>
       <c r="F11" s="2">
-        <v>15.07648635861851</v>
+        <v>15.08</v>
       </c>
       <c r="G11" s="2">
-        <v>17.101596148973901</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="H11" s="2">
-        <v>41.31707317073171</v>
+        <v>41.32</v>
       </c>
       <c r="I11" s="2">
-        <v>3.722572509457756</v>
+        <v>3.72</v>
       </c>
       <c r="J11" s="2">
-        <v>23.05019418240245</v>
+        <v>23.05</v>
       </c>
       <c r="K11" s="2">
         <v>30.02</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>39.841772151898716</v>
+        <v>39.840000000000003</v>
       </c>
       <c r="C12" s="2">
-        <v>21.838224340831221</v>
+        <v>21.84</v>
       </c>
       <c r="D12" s="2">
-        <v>46.52711703139866</v>
+        <v>46.53</v>
       </c>
       <c r="E12" s="2">
-        <v>55.295378022650773</v>
+        <v>55.3</v>
       </c>
       <c r="F12" s="2">
-        <v>16.669295063870049</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="G12" s="2">
-        <v>19.077780592855341</v>
+        <v>19.079999999999998</v>
       </c>
       <c r="H12" s="2">
-        <v>49.621951219512198</v>
+        <v>49.62</v>
       </c>
       <c r="I12" s="2">
-        <v>4.8776796973518266</v>
+        <v>4.88</v>
       </c>
       <c r="J12" s="2">
-        <v>30.888136312810779</v>
+        <v>30.89</v>
       </c>
       <c r="K12" s="2">
         <v>33.35</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>35.316455696202517</v>
+        <v>35.32</v>
       </c>
       <c r="C13" s="2">
-        <v>22.076567853418741</v>
+        <v>22.08</v>
       </c>
       <c r="D13" s="2">
-        <v>37.982873453853472</v>
+        <v>37.979999999999997</v>
       </c>
       <c r="E13" s="2">
-        <v>12.519130700948891</v>
+        <v>12.52</v>
       </c>
       <c r="F13" s="2">
-        <v>14.06718183251853</v>
+        <v>14.07</v>
       </c>
       <c r="G13" s="2">
-        <v>19.02710919685838</v>
+        <v>19.03</v>
       </c>
       <c r="H13" s="2">
-        <v>27.262195121951219</v>
+        <v>27.26</v>
       </c>
       <c r="I13" s="2">
-        <v>2.179066834804539</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="J13" s="2">
-        <v>26.046604371328058</v>
+        <v>26.05</v>
       </c>
       <c r="K13" s="2">
         <v>23.32</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>29.889240506329109</v>
+        <v>29.89</v>
       </c>
       <c r="C14" s="2">
-        <v>18.650379859973189</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="D14" s="2">
-        <v>35.204567078972403</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="E14" s="2">
-        <v>29.10927456382003</v>
+        <v>29.11</v>
       </c>
       <c r="F14" s="2">
-        <v>20.044157073016869</v>
+        <v>20.04</v>
       </c>
       <c r="G14" s="2">
-        <v>22.244742842665321</v>
+        <v>22.24</v>
       </c>
       <c r="H14" s="2">
-        <v>27.95121951219512</v>
+        <v>27.95</v>
       </c>
       <c r="I14" s="2">
-        <v>1.939470365699874</v>
+        <v>1.94</v>
       </c>
       <c r="J14" s="2">
-        <v>12.54383212131299</v>
+        <v>12.54</v>
       </c>
       <c r="K14" s="2">
         <v>23.64</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>21.898734177215189</v>
+        <v>21.9</v>
       </c>
       <c r="C15" s="2">
-        <v>14.24102487710412</v>
+        <v>14.24</v>
       </c>
       <c r="D15" s="2">
-        <v>30.06660323501427</v>
+        <v>30.07</v>
       </c>
       <c r="E15" s="2">
-        <v>30.93051729415367</v>
+        <v>30.93</v>
       </c>
       <c r="F15" s="2">
-        <v>8.9733480523576734</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="G15" s="2">
-        <v>12.79452748923233</v>
+        <v>12.79</v>
       </c>
       <c r="H15" s="2">
-        <v>19.33536585365853</v>
+        <v>19.34</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>10.62310026520626</v>
+        <v>10.62</v>
       </c>
       <c r="K15" s="2">
         <v>17.71</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>25.316455696202532</v>
+        <v>25.32</v>
       </c>
       <c r="C16" s="2">
-        <v>16.69894235066289</v>
+        <v>16.7</v>
       </c>
       <c r="D16" s="2">
-        <v>37.792578496669833</v>
+        <v>37.79</v>
       </c>
       <c r="E16" s="2">
-        <v>27.976737067646159</v>
+        <v>27.98</v>
       </c>
       <c r="F16" s="2">
-        <v>11.48083898438732</v>
+        <v>11.48</v>
       </c>
       <c r="G16" s="2">
-        <v>28.375981758297449</v>
+        <v>28.38</v>
       </c>
       <c r="H16" s="2">
-        <v>32.006097560975597</v>
+        <v>32.01</v>
       </c>
       <c r="I16" s="2">
-        <v>1.493064312736444</v>
+        <v>1.49</v>
       </c>
       <c r="J16" s="2">
-        <v>13.55857766418057</v>
+        <v>13.56</v>
       </c>
       <c r="K16" s="2">
         <v>22.55</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>12.37341772151899</v>
+        <v>12.37</v>
       </c>
       <c r="C17" s="2">
-        <v>6.5246536570832721</v>
+        <v>6.52</v>
       </c>
       <c r="D17" s="2">
-        <v>12.806850618458601</v>
+        <v>12.81</v>
       </c>
       <c r="E17" s="2">
-        <v>21.043771043771041</v>
+        <v>21.04</v>
       </c>
       <c r="F17" s="2">
-        <v>5.2830783788046043</v>
+        <v>5.28</v>
       </c>
       <c r="G17" s="2">
-        <v>9.9315936154041058</v>
+        <v>9.93</v>
       </c>
       <c r="H17" s="2">
-        <v>9.7256097560975618</v>
+        <v>9.73</v>
       </c>
       <c r="I17" s="2">
-        <v>0.13619167717528349</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J17" s="2">
-        <v>16.73036592591232</v>
+        <v>16.73</v>
       </c>
       <c r="K17" s="2">
         <v>11.12</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>45.617088607594937</v>
+        <v>45.62</v>
       </c>
       <c r="C18" s="2">
-        <v>26.247579323700279</v>
+        <v>26.25</v>
       </c>
       <c r="D18" s="2">
-        <v>40.799238820171247</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="E18" s="2">
-        <v>31.343740434649529</v>
+        <v>31.34</v>
       </c>
       <c r="F18" s="2">
-        <v>21.38463964674342</v>
+        <v>21.38</v>
       </c>
       <c r="G18" s="2">
-        <v>26.450468710412981</v>
+        <v>26.45</v>
       </c>
       <c r="H18" s="2">
-        <v>55.963414634146353</v>
+        <v>55.96</v>
       </c>
       <c r="I18" s="2">
-        <v>2.6607818411097099</v>
+        <v>2.66</v>
       </c>
       <c r="J18" s="2">
-        <v>31.270086223593101</v>
+        <v>31.27</v>
       </c>
       <c r="K18" s="2">
         <v>33.39</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>43.87658227848101</v>
+        <v>43.88</v>
       </c>
       <c r="C19" s="2">
-        <v>24.53448532697751</v>
+        <v>24.53</v>
       </c>
       <c r="D19" s="2">
-        <v>38.553758325404367</v>
+        <v>38.549999999999997</v>
       </c>
       <c r="E19" s="2">
-        <v>31.114172023262942</v>
+        <v>31.11</v>
       </c>
       <c r="F19" s="2">
-        <v>34.032486989433849</v>
+        <v>34.03</v>
       </c>
       <c r="G19" s="2">
-        <v>19.533823156827971</v>
+        <v>19.53</v>
       </c>
       <c r="H19" s="2">
-        <v>60.170731707317081</v>
+        <v>60.17</v>
       </c>
       <c r="I19" s="2">
-        <v>9.2358133669609082</v>
+        <v>9.24</v>
       </c>
       <c r="J19" s="2">
-        <v>39.823883472837743</v>
+        <v>39.82</v>
       </c>
       <c r="K19" s="2">
         <v>35.46</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>44.098101265822777</v>
+        <v>44.1</v>
       </c>
       <c r="C20" s="2">
-        <v>24.445106509757188</v>
+        <v>24.45</v>
       </c>
       <c r="D20" s="2">
-        <v>46.736441484300649</v>
+        <v>46.74</v>
       </c>
       <c r="E20" s="2">
-        <v>40.434649525558633</v>
+        <v>40.43</v>
       </c>
       <c r="F20" s="2">
-        <v>26.7623403248699</v>
+        <v>26.76</v>
       </c>
       <c r="G20" s="2">
-        <v>28.553331644286811</v>
+        <v>28.55</v>
       </c>
       <c r="H20" s="2">
-        <v>55.841463414634141</v>
+        <v>55.84</v>
       </c>
       <c r="I20" s="2">
-        <v>10.48928121059269</v>
+        <v>10.49</v>
       </c>
       <c r="J20" s="2">
-        <v>44.222260934963707</v>
+        <v>44.22</v>
       </c>
       <c r="K20" s="2">
         <v>37.31</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>32.341772151898738</v>
+        <v>32.340000000000003</v>
       </c>
       <c r="C21" s="2">
-        <v>18.412036347385669</v>
+        <v>18.41</v>
       </c>
       <c r="D21" s="2">
-        <v>37.202664129400567</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="E21" s="2">
-        <v>29.62962962962963</v>
+        <v>29.63</v>
       </c>
       <c r="F21" s="2">
-        <v>34.615991168585388</v>
+        <v>34.619999999999997</v>
       </c>
       <c r="G21" s="2">
-        <v>19.736508740815811</v>
+        <v>19.739999999999998</v>
       </c>
       <c r="H21" s="2">
-        <v>42.835365853658537</v>
+        <v>42.84</v>
       </c>
       <c r="I21" s="2">
-        <v>4.8575031525851191</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="J21" s="2">
-        <v>21.096615708637302</v>
+        <v>21.1</v>
       </c>
       <c r="K21" s="2">
         <v>28.74</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>29.999999999999989</v>
+        <v>30</v>
       </c>
       <c r="C22" s="2">
-        <v>21.28705496797259</v>
+        <v>21.29</v>
       </c>
       <c r="D22" s="2">
-        <v>35.071360608943863</v>
+        <v>35.07</v>
       </c>
       <c r="E22" s="2">
-        <v>62.917049280685653</v>
+        <v>62.92</v>
       </c>
       <c r="F22" s="2">
-        <v>27.62971140198707</v>
+        <v>27.63</v>
       </c>
       <c r="G22" s="2">
-        <v>23.942234608563471</v>
+        <v>23.94</v>
       </c>
       <c r="H22" s="2">
         <v>35.5</v>
       </c>
       <c r="I22" s="2">
-        <v>3.377049180327869</v>
+        <v>3.38</v>
       </c>
       <c r="J22" s="2">
-        <v>15.78511701373832</v>
+        <v>15.79</v>
       </c>
       <c r="K22" s="2">
         <v>30.42</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>48.196202531645568</v>
+        <v>48.2</v>
       </c>
       <c r="C23" s="2">
-        <v>28.45225681513481</v>
+        <v>28.45</v>
       </c>
       <c r="D23" s="2">
-        <v>55.642245480494758</v>
+        <v>55.64</v>
       </c>
       <c r="E23" s="2">
-        <v>47.842056932966031</v>
+        <v>47.84</v>
       </c>
       <c r="F23" s="2">
-        <v>29.806024286390159</v>
+        <v>29.81</v>
       </c>
       <c r="G23" s="2">
-        <v>15.50544717506968</v>
+        <v>15.51</v>
       </c>
       <c r="H23" s="2">
-        <v>55.353658536585371</v>
+        <v>55.35</v>
       </c>
       <c r="I23" s="2">
-        <v>21.477931904161409</v>
+        <v>21.48</v>
       </c>
       <c r="J23" s="2">
-        <v>20.074319762097769</v>
+        <v>20.07</v>
       </c>
       <c r="K23" s="2">
         <v>37.46</v>
       </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
